--- a/result/R101_Test.xlsx
+++ b/result/R101_Test.xlsx
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -452,98 +452,30 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1658.1</v>
+        <v>1662.43</v>
       </c>
       <c r="D4" s="3">
-        <v>1658.1</v>
+        <v>1662.43</v>
       </c>
       <c r="E4" s="3">
-        <v>111.73</v>
+        <v>140.66</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="3">
-        <v>2</v>
+      <c r="A5" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
       </c>
       <c r="C5" s="3">
-        <v>1676.99</v>
+        <v>1662.43</v>
       </c>
       <c r="D5" s="3">
-        <v>1676.99</v>
+        <v>1662.43</v>
       </c>
       <c r="E5" s="3">
-        <v>109.05</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1677.86</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1677.86</v>
-      </c>
-      <c r="E6" s="3">
-        <v>106.23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1688.8</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1688.8</v>
-      </c>
-      <c r="E7" s="3">
-        <v>110.35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1675.28</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1675.28</v>
-      </c>
-      <c r="E8" s="3">
-        <v>108.14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3">
-        <v>19</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1675.406</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1675.406</v>
-      </c>
-      <c r="E9" s="3">
-        <v>109.1</v>
+        <v>140.66</v>
       </c>
     </row>
   </sheetData>

--- a/result/R101_Test.xlsx
+++ b/result/R101_Test.xlsx
@@ -452,13 +452,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1662.43</v>
+        <v>1662.35</v>
       </c>
       <c r="D4" s="3">
-        <v>1662.43</v>
+        <v>1662.35</v>
       </c>
       <c r="E4" s="3">
-        <v>140.66</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -469,13 +469,13 @@
         <v>19</v>
       </c>
       <c r="C5" s="3">
-        <v>1662.43</v>
+        <v>1662.35</v>
       </c>
       <c r="D5" s="3">
-        <v>1662.43</v>
+        <v>1662.35</v>
       </c>
       <c r="E5" s="3">
-        <v>140.66</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/result/R101_Test.xlsx
+++ b/result/R101_Test.xlsx
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -449,16 +449,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3">
-        <v>1662.77</v>
+        <v>1676.84</v>
       </c>
       <c r="D4" s="3">
-        <v>1662.77</v>
+        <v>1676.84</v>
       </c>
       <c r="E4" s="3">
-        <v>71.55</v>
+        <v>112.06</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -466,16 +466,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1677.7</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3">
-        <v>1677.7</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3">
-        <v>72.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -483,33 +483,152 @@
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>1671.26</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3">
-        <v>1671.26</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3">
-        <v>85.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B7" s="3">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1670.576666666667</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1670.576666666667</v>
-      </c>
-      <c r="E7" s="3">
-        <v>76.66333333333334</v>
+      <c r="B10" s="3">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3">
+        <v>167.684</v>
+      </c>
+      <c r="D14" s="3">
+        <v>167.684</v>
+      </c>
+      <c r="E14" s="3">
+        <v>11.206</v>
       </c>
     </row>
   </sheetData>
